--- a/test_output2.xlsx
+++ b/test_output2.xlsx
@@ -4,18 +4,10 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Timeline" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Timeline" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>TBD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -390,17 +382,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A10:C11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <f>IF(ISNUMBER($C$10), $C$10+10, "TBD")</f>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <f>1+1</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
